--- a/outputs/btf-record-link/btf-record_Example-James-W-H-N-RT-wk-5.xlsx
+++ b/outputs/btf-record-link/btf-record_Example-James-W-H-N-RT-wk-5.xlsx
@@ -579,12 +579,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Water source</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>mL/day</t>
         </is>
@@ -655,7 +655,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Chart note</t>
         </is>
@@ -686,12 +686,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nutrient</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Target per day</t>
         </is>
@@ -742,32 +742,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Blend id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Blend name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Measured final volume (mL)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flow test date</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flow test result</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Flow test notes</t>
         </is>
@@ -828,47 +828,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Blend id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Blend name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>CNF food code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Food description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Counts as fluid</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Measure label</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Measure grams</t>
         </is>
@@ -1546,52 +1546,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Source type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Source id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Counts as fluid</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Measure label</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Measure grams</t>
         </is>
@@ -2224,17 +2224,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Food code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nutrient</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Per 100 g</t>
         </is>
@@ -2255,47 +2255,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nutrient</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Daily Total</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Per kg</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>% Target</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
@@ -2805,27 +2805,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nutrient</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Daily Total</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
@@ -3371,57 +3371,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Energy (kcal)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Protein (g)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Carbohydrate (g)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fat (g)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fluids provided (mL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Fibre (g)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sodium (mg)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Potassium (mg)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Calcium (mg)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Iron (mg)</t>
         </is>
